--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>encounterParticipant représente une personne impliquée dans la prise en charge du patient/usager, comme 
-par exemple, le professionnel co-responsable, le professionnel ayant fait l'admission ou encore le professionnel 
+    <t>encounterParticipant représente une personne impliquée dans la prise en charge du patient/usager, comme par exemple, le professionnel co-responsable, le professionnel ayant fait l'admission ou encore le professionnel 
 ayant donné son avis quant à la prise en charge.</t>
   </si>
   <si>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>encounterParticipant représente une personne impliquée dans la prise en charge du patient/usager, comme par exemple, le professionnel co-responsable, le professionnel ayant fait l'admission ou encore le professionnel 
-ayant donné son avis quant à la prise en charge.</t>
+    <t>L'élément de l'en-tête du CDA encounterParticipant permet de représenter la personne impliquée dans la prise en charge du patient/usager, comme par exemple, le professionnel co-responsable, le professionnel ayant fait l'admission ou encore le professionnel ayant donné son avis quant à la prise en charge.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
